--- a/data/trans_orig/P2A_fisi_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2A_fisi_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2007</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad física en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3666</t>
+          <t>3526</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14979</t>
+          <t>14353</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9547</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25673</t>
+          <t>25206</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16146</t>
+          <t>15103</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34400</t>
+          <t>33750</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>479085</t>
+          <t>479711</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>490398</t>
+          <t>490538</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>441816</t>
+          <t>442283</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>458218</t>
+          <t>457942</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>927153</t>
+          <t>927803</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>945407</t>
+          <t>946450</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9800</t>
+          <t>9899</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25304</t>
+          <t>25212</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9049</t>
+          <t>9264</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25481</t>
+          <t>24699</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22904</t>
+          <t>22270</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45028</t>
+          <t>43417</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>710185</t>
+          <t>710277</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>725689</t>
+          <t>725590</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>600013</t>
+          <t>600795</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>616445</t>
+          <t>616230</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1315954</t>
+          <t>1317565</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1338078</t>
+          <t>1338712</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,36%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18066</t>
+          <t>17676</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39672</t>
+          <t>39894</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21897</t>
+          <t>21777</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46707</t>
+          <t>44989</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45633</t>
+          <t>44584</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>76855</t>
+          <t>75978</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>598996</t>
+          <t>598774</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>620602</t>
+          <t>620992</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>643037</t>
+          <t>644755</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>667847</t>
+          <t>667967</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1251557</t>
+          <t>1252434</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1282779</t>
+          <t>1283828</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18777</t>
+          <t>18375</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39583</t>
+          <t>39451</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30859</t>
+          <t>32698</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57442</t>
+          <t>56652</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55935</t>
+          <t>54720</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>87215</t>
+          <t>89197</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>479564</t>
+          <t>479696</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>500370</t>
+          <t>500772</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>458200</t>
+          <t>458990</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>484783</t>
+          <t>482944</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>947574</t>
+          <t>945592</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>978854</t>
+          <t>980069</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,71%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25337</t>
+          <t>25651</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47844</t>
+          <t>49336</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22409</t>
+          <t>22724</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44872</t>
+          <t>46337</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52237</t>
+          <t>52500</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>82222</t>
+          <t>87641</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>338866</t>
+          <t>337374</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>361373</t>
+          <t>361059</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>359114</t>
+          <t>357649</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>381577</t>
+          <t>381262</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>708474</t>
+          <t>703055</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>738459</t>
+          <t>738196</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,36%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16674</t>
+          <t>16247</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36324</t>
+          <t>35742</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21091</t>
+          <t>22714</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40790</t>
+          <t>41076</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>42786</t>
+          <t>42718</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>71081</t>
+          <t>71878</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>256259</t>
+          <t>256841</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>275909</t>
+          <t>276336</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>302144</t>
+          <t>301858</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>321843</t>
+          <t>320220</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>564436</t>
+          <t>563639</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>592731</t>
+          <t>592799</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,28%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16185</t>
+          <t>16869</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33905</t>
+          <t>34552</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30578</t>
+          <t>29703</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55312</t>
+          <t>55335</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>51910</t>
+          <t>51766</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>81042</t>
+          <t>83252</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,31%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>175978</t>
+          <t>175331</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>193698</t>
+          <t>193014</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>278596</t>
+          <t>278573</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>303330</t>
+          <t>304205</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>462749</t>
+          <t>460539</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>491881</t>
+          <t>492025</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,48%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>139518</t>
+          <t>140911</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>191126</t>
+          <t>188514</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>183046</t>
+          <t>185394</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>240842</t>
+          <t>242778</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>338131</t>
+          <t>341330</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>415727</t>
+          <t>414212</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3085417</t>
+          <t>3088029</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3137025</t>
+          <t>3135632</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3138355</t>
+          <t>3136419</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3196151</t>
+          <t>3193803</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6240014</t>
+          <t>6241529</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6317610</t>
+          <t>6314411</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,87%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2012</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad física en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5786</t>
+          <t>5709</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20765</t>
+          <t>20417</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10921</t>
+          <t>10378</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29102</t>
+          <t>27355</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20234</t>
+          <t>19832</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41063</t>
+          <t>41326</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>433381</t>
+          <t>433729</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>448360</t>
+          <t>448437</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>401128</t>
+          <t>402875</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>419309</t>
+          <t>419852</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>843313</t>
+          <t>843050</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>864142</t>
+          <t>864544</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,76%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23905</t>
+          <t>23585</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47335</t>
+          <t>48410</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15700</t>
+          <t>15343</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37378</t>
+          <t>34955</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44838</t>
+          <t>44397</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74515</t>
+          <t>77449</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>639752</t>
+          <t>638677</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>663182</t>
+          <t>663502</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>572877</t>
+          <t>575300</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>594555</t>
+          <t>594912</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1222827</t>
+          <t>1219893</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1252504</t>
+          <t>1252945</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25812</t>
+          <t>24742</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50987</t>
+          <t>49083</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39548</t>
+          <t>39701</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68317</t>
+          <t>68357</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71083</t>
+          <t>72019</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>108850</t>
+          <t>110651</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>630876</t>
+          <t>632780</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>656051</t>
+          <t>657121</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>642533</t>
+          <t>642493</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>671302</t>
+          <t>671149</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1283862</t>
+          <t>1282061</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1321629</t>
+          <t>1320693</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,83%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28521</t>
+          <t>28788</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53726</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45938</t>
+          <t>44203</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76470</t>
+          <t>76540</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>80474</t>
+          <t>82071</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>122826</t>
+          <t>121218</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>560891</t>
+          <t>559288</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>586096</t>
+          <t>585829</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>539729</t>
+          <t>539659</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>570261</t>
+          <t>571996</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1107990</t>
+          <t>1109598</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1150342</t>
+          <t>1148745</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,33%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33663</t>
+          <t>34757</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60960</t>
+          <t>60885</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39086</t>
+          <t>38228</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67922</t>
+          <t>67604</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>79306</t>
+          <t>80213</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>117122</t>
+          <t>119857</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,66%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>368469</t>
+          <t>368544</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>395766</t>
+          <t>394672</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>379878</t>
+          <t>380196</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>408714</t>
+          <t>409572</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>760107</t>
+          <t>757372</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>797923</t>
+          <t>797016</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,86%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29463</t>
+          <t>29836</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>58019</t>
+          <t>57068</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28540</t>
+          <t>29054</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52444</t>
+          <t>53893</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>65338</t>
+          <t>66018</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>100366</t>
+          <t>102285</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,41%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>251767</t>
+          <t>252718</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>280323</t>
+          <t>279950</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>301552</t>
+          <t>300103</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>325456</t>
+          <t>324942</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>563416</t>
+          <t>561497</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>598444</t>
+          <t>597764</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,05%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27705</t>
+          <t>27992</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54497</t>
+          <t>53399</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>60363</t>
+          <t>60950</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>91867</t>
+          <t>93931</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>94454</t>
+          <t>94346</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>137054</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,45%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>195354</t>
+          <t>196452</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>222146</t>
+          <t>221859</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>297112</t>
+          <t>295048</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>328616</t>
+          <t>328029</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>500905</t>
+          <t>501776</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>544376</t>
+          <t>544484</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,23%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>219117</t>
+          <t>222019</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>283385</t>
+          <t>282813</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>287725</t>
+          <t>289062</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>357100</t>
+          <t>360613</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>527507</t>
+          <t>527858</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>620899</t>
+          <t>621491</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3143394</t>
+          <t>3143966</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3207662</t>
+          <t>3204760</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3201209</t>
+          <t>3197696</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3270584</t>
+          <t>3269247</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6364189</t>
+          <t>6363597</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6457581</t>
+          <t>6457230</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,44%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2016</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad física en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6966</t>
+          <t>7240</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21943</t>
+          <t>22677</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3811</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15817</t>
+          <t>15326</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13689</t>
+          <t>12973</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31853</t>
+          <t>31533</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>397520</t>
+          <t>396786</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>412497</t>
+          <t>412223</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>379938</t>
+          <t>380429</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>391944</t>
+          <t>391750</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>783365</t>
+          <t>783685</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>801529</t>
+          <t>802245</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10891</t>
+          <t>11256</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26729</t>
+          <t>26958</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6794</t>
+          <t>7147</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21352</t>
+          <t>21601</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,47 +7084,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
+          <t>3,83%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>30953</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>21379</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>43741</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>3,79%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>30953</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>21246</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>42915</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>563767</t>
+          <t>563538</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>579605</t>
+          <t>579240</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>542192</t>
+          <t>541943</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>556750</t>
+          <t>556397</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,47 +7197,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
+          <t>96,17%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>98,73%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1115</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1123087</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>1110299</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>1132661</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>97,32%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>96,21%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>98,79%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1115</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1123087</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1111125</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1132794</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>97,32%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>96,28%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15647</t>
+          <t>15816</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35098</t>
+          <t>35688</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17634</t>
+          <t>17687</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35902</t>
+          <t>36584</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37014</t>
+          <t>37060</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65400</t>
+          <t>65263</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>633999</t>
+          <t>633409</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>653450</t>
+          <t>653281</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>625484</t>
+          <t>624802</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>643752</t>
+          <t>643699</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1265083</t>
+          <t>1265220</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1293469</t>
+          <t>1293423</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33831</t>
+          <t>34426</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62169</t>
+          <t>61220</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32621</t>
+          <t>33478</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57359</t>
+          <t>60198</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>73690</t>
+          <t>73988</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>110879</t>
+          <t>112621</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>583879</t>
+          <t>584828</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>612217</t>
+          <t>611622</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>591718</t>
+          <t>588879</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>616456</t>
+          <t>615599</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1184246</t>
+          <t>1182504</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1221435</t>
+          <t>1221137</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30387</t>
+          <t>30445</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56191</t>
+          <t>56223</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50577</t>
+          <t>51074</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>82369</t>
+          <t>82164</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>88770</t>
+          <t>86202</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>130515</t>
+          <t>128506</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,18%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>421727</t>
+          <t>421695</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>447531</t>
+          <t>447473</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>414480</t>
+          <t>414685</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>446272</t>
+          <t>445775</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>844252</t>
+          <t>846261</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>885997</t>
+          <t>888565</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,16%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17496</t>
+          <t>17091</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35869</t>
+          <t>36413</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21756</t>
+          <t>22555</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43285</t>
+          <t>44809</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>43015</t>
+          <t>45147</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>72331</t>
+          <t>72976</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>298461</t>
+          <t>297917</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>316834</t>
+          <t>317239</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>334477</t>
+          <t>332953</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>356006</t>
+          <t>355207</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>639761</t>
+          <t>639116</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>669077</t>
+          <t>666945</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,66%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11795</t>
+          <t>12438</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27906</t>
+          <t>28745</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40700</t>
+          <t>42456</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>73811</t>
+          <t>75058</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>60271</t>
+          <t>58928</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>95253</t>
+          <t>93383</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,21%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>229092</t>
+          <t>228253</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>245203</t>
+          <t>244560</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>326358</t>
+          <t>325111</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>359469</t>
+          <t>357713</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>561914</t>
+          <t>563784</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>596896</t>
+          <t>598239</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>91,03%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>161060</t>
+          <t>162097</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>215899</t>
+          <t>216780</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>214419</t>
+          <t>215180</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>275554</t>
+          <t>277386</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>392163</t>
+          <t>389233</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>478357</t>
+          <t>476535</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3178451</t>
+          <t>3177570</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3233290</t>
+          <t>3232253</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3268988</t>
+          <t>3267156</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3330123</t>
+          <t>3329362</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6460535</t>
+          <t>6462357</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6546729</t>
+          <t>6549659</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2023</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad física en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9326</t>
+          <t>8956</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36254</t>
+          <t>35071</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11740</t>
+          <t>11465</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35058</t>
+          <t>34436</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24356</t>
+          <t>25254</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60645</t>
+          <t>60125</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>363733</t>
+          <t>364916</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>390661</t>
+          <t>391031</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>278142</t>
+          <t>278764</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>301460</t>
+          <t>301735</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>652542</t>
+          <t>653062</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>688831</t>
+          <t>687933</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26503</t>
+          <t>26514</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61633</t>
+          <t>60518</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7458</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24560</t>
+          <t>25606</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38799</t>
+          <t>39560</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>78985</t>
+          <t>79778</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>361914</t>
+          <t>363029</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>397044</t>
+          <t>397033</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>487533</t>
+          <t>486487</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>504635</t>
+          <t>503760</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>856655</t>
+          <t>855862</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>896841</t>
+          <t>896080</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,77%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12341</t>
+          <t>12077</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30404</t>
+          <t>29790</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22055</t>
+          <t>21561</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41321</t>
+          <t>42702</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>39095</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65429</t>
+          <t>65115</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>505934</t>
+          <t>506548</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>523997</t>
+          <t>524261</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>550681</t>
+          <t>549300</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>569947</t>
+          <t>570441</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1062911</t>
+          <t>1063225</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1089913</t>
+          <t>1089245</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28813</t>
+          <t>28922</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>100876</t>
+          <t>99868</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50023</t>
+          <t>49235</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76103</t>
+          <t>75332</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>77798</t>
+          <t>79605</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>162358</t>
+          <t>163737</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>786910</t>
+          <t>787918</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>858973</t>
+          <t>858864</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>636778</t>
+          <t>637549</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>662858</t>
+          <t>663646</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1438309</t>
+          <t>1436930</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1522869</t>
+          <t>1521062</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,03%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>75081</t>
+          <t>74670</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>109394</t>
+          <t>107001</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>46536</t>
+          <t>47236</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67550</t>
+          <t>67245</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>128588</t>
+          <t>128586</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>166197</t>
+          <t>167792</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11132,7 +11132,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,13%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>451840</t>
+          <t>454233</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>486153</t>
+          <t>486564</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>480355</t>
+          <t>480660</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>501369</t>
+          <t>500669</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>942942</t>
+          <t>941347</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>980551</t>
+          <t>980553</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39341</t>
+          <t>39539</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>61591</t>
+          <t>59957</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>82713</t>
+          <t>81594</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>461540</t>
+          <t>446265</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>130901</t>
+          <t>130037</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>612562</t>
+          <t>618118</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>63,3%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>306574</t>
+          <t>308208</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>328824</t>
+          <t>328626</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>146828</t>
+          <t>162103</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>525655</t>
+          <t>526774</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>363971</t>
+          <t>358415</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>845632</t>
+          <t>846496</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,68%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>64749</t>
+          <t>64383</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>88004</t>
+          <t>88933</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>118207</t>
+          <t>120073</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>146033</t>
+          <t>147699</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>191491</t>
+          <t>191248</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>228637</t>
+          <t>226993</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,03%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>194755</t>
+          <t>193826</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>218010</t>
+          <t>218376</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>279798</t>
+          <t>278132</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>307624</t>
+          <t>305758</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>479953</t>
+          <t>481597</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>517099</t>
+          <t>517342</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>73,01%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>288845</t>
+          <t>280643</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>406715</t>
+          <t>412039</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>390677</t>
+          <t>390238</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1159719</t>
+          <t>1157341</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>739944</t>
+          <t>736831</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1622589</t>
+          <t>1507037</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>21,01%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3053102</t>
+          <t>3047778</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3170972</t>
+          <t>3179174</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2552561</t>
+          <t>2554939</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3321603</t>
+          <t>3322042</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5549508</t>
+          <t>5665060</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6432153</t>
+          <t>6435266</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,73%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_fisi_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2A_fisi_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3526</t>
+          <t>3601</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14353</t>
+          <t>14463</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9547</t>
+          <t>9104</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25206</t>
+          <t>24686</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15103</t>
+          <t>15251</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33750</t>
+          <t>34733</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>479711</t>
+          <t>479601</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>490538</t>
+          <t>490463</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>442283</t>
+          <t>442803</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>457942</t>
+          <t>458385</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>927803</t>
+          <t>926820</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>946450</t>
+          <t>946302</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9899</t>
+          <t>9859</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25212</t>
+          <t>26972</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9264</t>
+          <t>9690</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24699</t>
+          <t>26029</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22270</t>
+          <t>23149</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43417</t>
+          <t>44456</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>710277</t>
+          <t>708517</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>725590</t>
+          <t>725630</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>600795</t>
+          <t>599465</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>616230</t>
+          <t>615804</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1317565</t>
+          <t>1316526</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1338712</t>
+          <t>1337833</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,3%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17676</t>
+          <t>17538</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39894</t>
+          <t>39762</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21777</t>
+          <t>21863</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44989</t>
+          <t>46136</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44584</t>
+          <t>44463</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75978</t>
+          <t>77160</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>598774</t>
+          <t>598906</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>620992</t>
+          <t>621130</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>644755</t>
+          <t>643608</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>667967</t>
+          <t>667881</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1252434</t>
+          <t>1251252</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1283828</t>
+          <t>1283949</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18375</t>
+          <t>18119</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39451</t>
+          <t>41001</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32698</t>
+          <t>32604</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56652</t>
+          <t>56987</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54720</t>
+          <t>55640</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>89197</t>
+          <t>89528</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>479696</t>
+          <t>478146</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>500772</t>
+          <t>501028</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>458990</t>
+          <t>458655</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>482944</t>
+          <t>483038</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>945592</t>
+          <t>945261</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>980069</t>
+          <t>979149</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,62%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25651</t>
+          <t>24811</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49336</t>
+          <t>47705</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22724</t>
+          <t>22254</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46337</t>
+          <t>45656</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52500</t>
+          <t>53304</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>87641</t>
+          <t>84602</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>337374</t>
+          <t>339005</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>361059</t>
+          <t>361899</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>357649</t>
+          <t>358330</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>381262</t>
+          <t>381732</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>703055</t>
+          <t>706094</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>738196</t>
+          <t>737392</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,26%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16247</t>
+          <t>17178</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35742</t>
+          <t>36120</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22714</t>
+          <t>22173</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41076</t>
+          <t>42277</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>42718</t>
+          <t>42622</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>71878</t>
+          <t>70529</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>256841</t>
+          <t>256463</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>276336</t>
+          <t>275405</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>301858</t>
+          <t>300657</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>320220</t>
+          <t>320761</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>563639</t>
+          <t>564988</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>592799</t>
+          <t>592895</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,29%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16869</t>
+          <t>16485</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34552</t>
+          <t>33917</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29703</t>
+          <t>30226</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55335</t>
+          <t>56510</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>51766</t>
+          <t>53018</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>83252</t>
+          <t>82405</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>175331</t>
+          <t>175966</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>193014</t>
+          <t>193398</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>278573</t>
+          <t>277398</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>304205</t>
+          <t>303682</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>460539</t>
+          <t>461386</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>492025</t>
+          <t>490773</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,25%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>140911</t>
+          <t>138475</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>188514</t>
+          <t>189999</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>185394</t>
+          <t>182438</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>242778</t>
+          <t>241226</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>341330</t>
+          <t>338008</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>414212</t>
+          <t>411953</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3088029</t>
+          <t>3086544</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3135632</t>
+          <t>3138068</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3136419</t>
+          <t>3137971</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3193803</t>
+          <t>3196759</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6241529</t>
+          <t>6243788</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6314411</t>
+          <t>6317733</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,92%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5709</t>
+          <t>5810</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20417</t>
+          <t>22293</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10378</t>
+          <t>11033</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27355</t>
+          <t>27586</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19832</t>
+          <t>19285</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41326</t>
+          <t>41086</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>433729</t>
+          <t>431853</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>448437</t>
+          <t>448336</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>402875</t>
+          <t>402644</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>419852</t>
+          <t>419197</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>843050</t>
+          <t>843290</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>864544</t>
+          <t>865091</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,82%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23585</t>
+          <t>24092</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48410</t>
+          <t>46769</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15343</t>
+          <t>15618</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34955</t>
+          <t>36967</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44397</t>
+          <t>44602</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>77449</t>
+          <t>74129</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>638677</t>
+          <t>640318</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>663502</t>
+          <t>662995</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>575300</t>
+          <t>573288</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>594912</t>
+          <t>594637</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1219893</t>
+          <t>1223213</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1252945</t>
+          <t>1252740</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,56%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24742</t>
+          <t>25776</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49083</t>
+          <t>50169</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39701</t>
+          <t>38954</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68357</t>
+          <t>68231</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>72019</t>
+          <t>70896</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>110651</t>
+          <t>108088</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>632780</t>
+          <t>631694</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>657121</t>
+          <t>656087</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>642493</t>
+          <t>642619</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>671149</t>
+          <t>671896</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1282061</t>
+          <t>1284624</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1320693</t>
+          <t>1321816</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,91%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28788</t>
+          <t>28831</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>54280</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44203</t>
+          <t>46191</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76540</t>
+          <t>78736</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82071</t>
+          <t>81529</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>121218</t>
+          <t>126094</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,24%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>559288</t>
+          <t>560337</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>585829</t>
+          <t>585786</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>539659</t>
+          <t>537463</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>571996</t>
+          <t>570008</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1109598</t>
+          <t>1104722</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1148745</t>
+          <t>1149287</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,38%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34757</t>
+          <t>34627</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60885</t>
+          <t>61161</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38228</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67604</t>
+          <t>66624</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>80213</t>
+          <t>80575</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>119857</t>
+          <t>119659</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,64%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>368544</t>
+          <t>368268</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>394672</t>
+          <t>394802</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>380196</t>
+          <t>381176</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>409572</t>
+          <t>409530</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>757372</t>
+          <t>757570</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>797016</t>
+          <t>796654</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,81%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29836</t>
+          <t>30896</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>57068</t>
+          <t>57666</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29054</t>
+          <t>29737</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53893</t>
+          <t>55865</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>66018</t>
+          <t>67791</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>102285</t>
+          <t>102494</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,44%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>252718</t>
+          <t>252120</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>279950</t>
+          <t>278890</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>300103</t>
+          <t>298131</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>324942</t>
+          <t>324259</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>561497</t>
+          <t>561288</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>597764</t>
+          <t>595991</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>89,79%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27992</t>
+          <t>27434</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53399</t>
+          <t>53681</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>60950</t>
+          <t>60727</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>93931</t>
+          <t>93627</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>94346</t>
+          <t>96310</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>137054</t>
+          <t>137891</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,58%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>196452</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>221859</t>
+          <t>222417</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>295048</t>
+          <t>295352</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>328029</t>
+          <t>328252</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>501776</t>
+          <t>500939</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>544484</t>
+          <t>542520</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>84,92%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>222019</t>
+          <t>218116</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>282813</t>
+          <t>285421</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>289062</t>
+          <t>287533</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>360613</t>
+          <t>360504</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>527858</t>
+          <t>527790</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>621491</t>
+          <t>627280</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3143966</t>
+          <t>3141358</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3204760</t>
+          <t>3208663</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3197696</t>
+          <t>3197805</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3269247</t>
+          <t>3270776</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6363597</t>
+          <t>6357808</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6457230</t>
+          <t>6457298</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22677</t>
+          <t>22569</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>3827</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15326</t>
+          <t>16215</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12973</t>
+          <t>14308</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31533</t>
+          <t>31111</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>396786</t>
+          <t>396894</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>412223</t>
+          <t>412647</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>380429</t>
+          <t>379540</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>391750</t>
+          <t>391928</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>783685</t>
+          <t>784107</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>802245</t>
+          <t>800910</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11256</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26958</t>
+          <t>29047</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7147</t>
+          <t>7516</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21601</t>
+          <t>22065</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21379</t>
+          <t>21155</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43741</t>
+          <t>42690</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>563538</t>
+          <t>561449</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>579240</t>
+          <t>579308</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>541943</t>
+          <t>541479</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>556397</t>
+          <t>556028</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1110299</t>
+          <t>1111350</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1132661</t>
+          <t>1132885</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15816</t>
+          <t>15431</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35688</t>
+          <t>35303</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17687</t>
+          <t>16972</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36584</t>
+          <t>35988</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37060</t>
+          <t>37490</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65263</t>
+          <t>66088</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>633409</t>
+          <t>633794</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>653281</t>
+          <t>653666</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>624802</t>
+          <t>625398</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>643699</t>
+          <t>644414</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1265220</t>
+          <t>1264395</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1293423</t>
+          <t>1292993</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34426</t>
+          <t>33711</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>61220</t>
+          <t>60115</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33478</t>
+          <t>33012</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60198</t>
+          <t>59042</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>73988</t>
+          <t>72810</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>112621</t>
+          <t>114137</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>584828</t>
+          <t>585933</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>611622</t>
+          <t>612337</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>588879</t>
+          <t>590035</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>615599</t>
+          <t>616065</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1182504</t>
+          <t>1180988</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1221137</t>
+          <t>1222315</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,38%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30445</t>
+          <t>30069</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56223</t>
+          <t>56598</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51074</t>
+          <t>50190</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>82164</t>
+          <t>81122</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>86202</t>
+          <t>87184</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>128506</t>
+          <t>129803</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,32%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>421695</t>
+          <t>421320</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>447473</t>
+          <t>447849</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>414685</t>
+          <t>415727</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>445775</t>
+          <t>446659</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>846261</t>
+          <t>844964</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>888565</t>
+          <t>887583</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,06%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17091</t>
+          <t>17591</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36413</t>
+          <t>36302</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22555</t>
+          <t>21561</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>44809</t>
+          <t>42712</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45147</t>
+          <t>44829</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>72976</t>
+          <t>76420</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,73%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>297917</t>
+          <t>298028</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>317239</t>
+          <t>316739</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>332953</t>
+          <t>335050</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>355207</t>
+          <t>356201</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>639116</t>
+          <t>635672</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>666945</t>
+          <t>667263</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,7%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12438</t>
+          <t>12201</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28745</t>
+          <t>27911</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>42456</t>
+          <t>42352</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>75058</t>
+          <t>74676</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>58928</t>
+          <t>59805</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>93383</t>
+          <t>95242</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,49%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>228253</t>
+          <t>229087</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>244560</t>
+          <t>244797</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>325111</t>
+          <t>325493</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>357713</t>
+          <t>357817</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>563784</t>
+          <t>561925</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>598239</t>
+          <t>597362</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>90,9%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>162097</t>
+          <t>163918</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>216780</t>
+          <t>217219</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>215180</t>
+          <t>213063</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>277386</t>
+          <t>274503</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>389233</t>
+          <t>392156</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>476535</t>
+          <t>470234</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3177570</t>
+          <t>3177131</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3232253</t>
+          <t>3230432</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3267156</t>
+          <t>3270039</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3329362</t>
+          <t>3331479</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6462357</t>
+          <t>6468658</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6549659</t>
+          <t>6546736</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,35%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19158</t>
+          <t>18273</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8956</t>
+          <t>8522</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35071</t>
+          <t>34988</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>21093</t>
+          <t>24846</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11465</t>
+          <t>13812</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34436</t>
+          <t>40886</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>40251</t>
+          <t>43119</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25254</t>
+          <t>27699</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60125</t>
+          <t>61953</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>380829</t>
+          <t>389520</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>364916</t>
+          <t>372805</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>391031</t>
+          <t>399271</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>292107</t>
+          <t>337666</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>278764</t>
+          <t>321626</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>301735</t>
+          <t>348700</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>672936</t>
+          <t>727186</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>653062</t>
+          <t>708352</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>687933</t>
+          <t>742606</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,4%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40804</t>
+          <t>40532</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26514</t>
+          <t>26702</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60518</t>
+          <t>60913</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15461</t>
+          <t>19951</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>12285</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25606</t>
+          <t>30338</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>56266</t>
+          <t>60483</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39560</t>
+          <t>44257</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>79778</t>
+          <t>83003</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>382743</t>
+          <t>436358</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>363029</t>
+          <t>415977</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>397033</t>
+          <t>450188</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>496632</t>
+          <t>481782</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>486487</t>
+          <t>471395</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>503760</t>
+          <t>489448</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>879374</t>
+          <t>918140</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>855862</t>
+          <t>895620</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>896080</t>
+          <t>934366</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,48%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>19471</t>
+          <t>21782</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12077</t>
+          <t>13391</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29790</t>
+          <t>33137</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>31741</t>
+          <t>36861</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21561</t>
+          <t>27360</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42702</t>
+          <t>47744</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>51212</t>
+          <t>58643</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39095</t>
+          <t>45426</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65115</t>
+          <t>73939</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>516867</t>
+          <t>599055</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>506548</t>
+          <t>587700</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>524261</t>
+          <t>607446</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>560261</t>
+          <t>586332</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>549300</t>
+          <t>575449</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>570441</t>
+          <t>595833</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1077128</t>
+          <t>1185386</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1063225</t>
+          <t>1170090</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1089245</t>
+          <t>1198603</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,35%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>66671</t>
+          <t>71065</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28922</t>
+          <t>56947</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>99868</t>
+          <t>90597</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>62903</t>
+          <t>68903</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49235</t>
+          <t>57293</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75332</t>
+          <t>81215</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>129574</t>
+          <t>139968</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>79605</t>
+          <t>118849</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>163737</t>
+          <t>161078</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>821115</t>
+          <t>629552</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>787918</t>
+          <t>610020</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>858864</t>
+          <t>643670</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>649978</t>
+          <t>667983</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>637549</t>
+          <t>655671</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>663646</t>
+          <t>679593</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1471093</t>
+          <t>1297536</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1436930</t>
+          <t>1276426</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1521062</t>
+          <t>1318655</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>91,73%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>90296</t>
+          <t>95379</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>74670</t>
+          <t>78512</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>107001</t>
+          <t>113549</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>57195</t>
+          <t>67241</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47236</t>
+          <t>55807</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67245</t>
+          <t>80523</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>147490</t>
+          <t>162621</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>128586</t>
+          <t>141817</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>167792</t>
+          <t>185411</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,22%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>470938</t>
+          <t>513967</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>454233</t>
+          <t>495797</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>486564</t>
+          <t>530834</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>490710</t>
+          <t>541614</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>480660</t>
+          <t>528332</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>500669</t>
+          <t>553048</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>961649</t>
+          <t>1055581</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>941347</t>
+          <t>1032791</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>980553</t>
+          <t>1076385</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,36%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>49718</t>
+          <t>54612</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39539</t>
+          <t>43831</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>59957</t>
+          <t>66692</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>262876</t>
+          <t>64205</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>81594</t>
+          <t>53875</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>446265</t>
+          <t>75550</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>312594</t>
+          <t>118817</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>130037</t>
+          <t>103385</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>618118</t>
+          <t>136059</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>16,08%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>318447</t>
+          <t>352468</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>308208</t>
+          <t>340388</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>328626</t>
+          <t>363249</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>345492</t>
+          <t>374961</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>162103</t>
+          <t>363616</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>526774</t>
+          <t>385291</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>663939</t>
+          <t>727429</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>358415</t>
+          <t>710187</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>846496</t>
+          <t>742861</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>87,78%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>75873</t>
+          <t>82032</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>64383</t>
+          <t>69498</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>88933</t>
+          <t>95350</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>132840</t>
+          <t>145408</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>120073</t>
+          <t>130611</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>147699</t>
+          <t>160746</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>208713</t>
+          <t>227441</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>191248</t>
+          <t>207705</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>226993</t>
+          <t>246137</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>31,77%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>206886</t>
+          <t>228166</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>193826</t>
+          <t>214848</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>218376</t>
+          <t>240700</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>292991</t>
+          <t>319201</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>278132</t>
+          <t>303863</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>305758</t>
+          <t>333998</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>499877</t>
+          <t>547366</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>481597</t>
+          <t>528670</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>517342</t>
+          <t>567102</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>73,19%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>361991</t>
+          <t>383676</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>280643</t>
+          <t>346484</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>412039</t>
+          <t>422103</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>584109</t>
+          <t>427416</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>390238</t>
+          <t>398113</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1157341</t>
+          <t>463994</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>946100</t>
+          <t>811091</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>736831</t>
+          <t>764914</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1507037</t>
+          <t>862677</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3097826</t>
+          <t>3149086</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3047778</t>
+          <t>3110659</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3179174</t>
+          <t>3186278</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3128171</t>
+          <t>3309538</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2554939</t>
+          <t>3272960</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3322042</t>
+          <t>3338841</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6225997</t>
+          <t>6458625</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5665060</t>
+          <t>6407039</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6435266</t>
+          <t>6504802</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,48%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">

--- a/data/trans_orig/P2A_fisi_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2A_fisi_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad física en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad física en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad física en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad física en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
